--- a/data/homes.xlsx
+++ b/data/homes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_bunyodkorhouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56CCEF77-BD12-4974-A9A9-A7026886D1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742BFFE2-235A-4FFB-9EB2-497F1EA4EB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{62441126-7CE5-4CDE-A799-90A69E79E000}"/>
   </bookViews>
@@ -533,9 +533,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C0DFFC-2F8A-4B53-B216-FC034C48B240}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="17.77734375" customWidth="1"/>
     <col min="4" max="4" width="27.21875" customWidth="1"/>
@@ -1324,6 +1325,74 @@
         <v>7000000</v>
       </c>
     </row>
+    <row r="47" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46</v>
+      </c>
+      <c r="C47" s="3">
+        <v>59</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2</v>
+      </c>
+      <c r="E47" s="3">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B48" s="5">
+        <v>47</v>
+      </c>
+      <c r="C48" s="5">
+        <v>59</v>
+      </c>
+      <c r="D48" s="5">
+        <v>2</v>
+      </c>
+      <c r="E48" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B49" s="5">
+        <v>48</v>
+      </c>
+      <c r="C49" s="5">
+        <v>59</v>
+      </c>
+      <c r="D49" s="5">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="6">
+        <v>-1</v>
+      </c>
+      <c r="B50" s="7">
+        <v>49</v>
+      </c>
+      <c r="C50" s="7">
+        <v>59</v>
+      </c>
+      <c r="D50" s="7">
+        <v>2</v>
+      </c>
+      <c r="E50" s="7">
+        <v>7000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
